--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260909.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260909.xlsx
@@ -909,17 +909,17 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>3,413,000</t>
+          <t>5,270,520</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>5,270,520</t>
+          <t>3,413,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>1,992,587</t>
+          <t>137,921</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>137,921</t>
+          <t>1,992,587</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -1283,17 +1283,17 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2313</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>華通</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,823,000</t>
+          <t>5,691,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,206,000</t>
+          <t>374,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>華通</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,691,000</t>
+          <t>1,823,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>374,000</t>
+          <t>3,206,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2409</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>友達</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>10,546,121</t>
+          <t>931,659</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2409</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>友達</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>931,659</t>
+          <t>10,546,121</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1679,17 +1679,17 @@
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>2,179,107</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>2,179,107</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1723,17 +1723,17 @@
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>微星</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>1,179,076</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>微星</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>1,179,076</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>4,934,956</t>
+          <t>772,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>318,000</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>318,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>495,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>772,000</t>
+          <t>495,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>226,000</t>
+          <t>4,934,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>1,707,640</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>1,707,640</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>170,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>329,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>998,121</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>170,000</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>329,000</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2075,17 +2075,17 @@
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>998,121</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
